--- a/projetos/OBRA_TMULT/04_PRODUCAO_E_AVANCO/PAINEL_RDOS_OBRA.xlsx
+++ b/projetos/OBRA_TMULT/04_PRODUCAO_E_AVANCO/PAINEL_RDOS_OBRA.xlsx
@@ -32,7 +32,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -102,7 +102,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -132,37 +132,23 @@
         <color rgb="00DDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="001B365D"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom style="double">
         <color rgb="001B365D"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E0E0E0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -174,89 +160,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -649,6 +597,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -699,6 +648,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -938,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1386,134 +1337,6 @@
       <c r="M9" s="27" t="n"/>
       <c r="N9" s="27" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>RDO-007</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>Ensolarado</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t>Ensolarado</t>
-        </is>
-      </c>
-      <c r="F10" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="33" t="n">
-        <v>16</v>
-      </c>
-      <c r="I10" s="34">
-        <f>G10+H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="35">
-        <f>(I10*8.8)-(F10*I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="31" t="inlineStr">
-        <is>
-          <t>EAP 1.3 / Fundações e Estrutura</t>
-        </is>
-      </c>
-      <c r="L10" s="31" t="inlineStr">
-        <is>
-          <t>FVS-02</t>
-        </is>
-      </c>
-      <c r="M10" s="36" t="inlineStr">
-        <is>
-          <t>🟢 Aprovado</t>
-        </is>
-      </c>
-      <c r="N10" s="31" t="inlineStr">
-        <is>
-          <t>RDO 29/09/2026: 8 pedreiros, 6 serventes e 2 carpinteiros. Clima bom de sol de manha e tarde. Escavacao sapatas S11 a S20. FVS-02 aprovada com sucesso. Sem paralisações.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
-        <is>
-          <t>RDO-008</t>
-        </is>
-      </c>
-      <c r="B11" s="37" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="D11" s="38" t="inlineStr">
-        <is>
-          <t>Ensolarado</t>
-        </is>
-      </c>
-      <c r="E11" s="38" t="inlineStr">
-        <is>
-          <t>Ensolarado</t>
-        </is>
-      </c>
-      <c r="F11" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="I11" s="41">
-        <f>G11+H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="42">
-        <f>(I11*8.8)-(F11*I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="38" t="inlineStr">
-        <is>
-          <t>EAP 1.3 / Fundações e Estrutura</t>
-        </is>
-      </c>
-      <c r="L11" s="38" t="inlineStr">
-        <is>
-          <t>FVS-02</t>
-        </is>
-      </c>
-      <c r="M11" s="43" t="inlineStr">
-        <is>
-          <t>🟢 Aprovado</t>
-        </is>
-      </c>
-      <c r="N11" s="38" t="inlineStr">
-        <is>
-          <t>RDO 11/09/2026: 8 pedreiros, 6 serventes e 2 carpinteiros. Clima de sol manha e tarde. Escavacao sapatas S21 a S28. FVS-02 aprovada com sucesso. Sem paralisacoes.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
